--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136855813</v>
       </c>
       <c r="B2" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136855813</v>
       </c>
       <c r="B2" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136855813</v>
       </c>
       <c r="B2" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136855813</v>
       </c>
       <c r="B2" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136855813</v>
       </c>
       <c r="B2" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39572-2026 artfynd.xlsx
+++ b/artfynd/A 39572-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136856031</v>
       </c>
       <c r="B3" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136856333</v>
       </c>
       <c r="B4" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>136856628</v>
       </c>
       <c r="B5" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
